--- a/data/P1/P1T2_BQ4.xlsx
+++ b/data/P1/P1T2_BQ4.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BDB213-D677-364B-8C41-58F8E8866908}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC30F98-BEE0-B249-AE4A-51AA309A18BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="29700" yWindow="4160" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -157,6 +158,22 @@
   </si>
   <si>
     <t>洪水；淹水</t>
+  </si>
+  <si>
+    <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sentence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No sentences</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>沒有句子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -806,4 +823,31 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7BD3983-DD53-464F-AB4D-2830704BE29B}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/P1/P1T2_BQ4.xlsx
+++ b/data/P1/P1T2_BQ4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CC30F98-BEE0-B249-AE4A-51AA309A18BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2E4E11-8F95-4546-85BC-A9615BF2EC45}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29700" yWindow="4160" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="82">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -174,13 +174,118 @@
   <si>
     <t>沒有句子</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>phonetics</t>
+  </si>
+  <si>
+    <t>syllable</t>
+  </si>
+  <si>
+    <t>/sprɪŋ/</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>/ˈsʌmə(r)/</t>
+  </si>
+  <si>
+    <t>sum-mer</t>
+  </si>
+  <si>
+    <t>/fɔːl/</t>
+  </si>
+  <si>
+    <t>/ˈwɪntə(r)/</t>
+  </si>
+  <si>
+    <t>win-ter</t>
+  </si>
+  <si>
+    <t>/wɔːm/</t>
+  </si>
+  <si>
+    <t>/hɒt/</t>
+  </si>
+  <si>
+    <t>/kuːl/</t>
+  </si>
+  <si>
+    <t>/kəʊld/</t>
+  </si>
+  <si>
+    <t>/reɪn/</t>
+  </si>
+  <si>
+    <t>/ˈweðə(r)/</t>
+  </si>
+  <si>
+    <t>wea-ther</t>
+  </si>
+  <si>
+    <t>/ˈsnəʊi/</t>
+  </si>
+  <si>
+    <t>snow-y</t>
+  </si>
+  <si>
+    <t>/ˈklaʊdi/</t>
+  </si>
+  <si>
+    <t>cloud-y</t>
+  </si>
+  <si>
+    <t>/ˈsʌni/</t>
+  </si>
+  <si>
+    <t>sun-ny</t>
+  </si>
+  <si>
+    <t>/ˈwɪndi/</t>
+  </si>
+  <si>
+    <t>wind-y</t>
+  </si>
+  <si>
+    <t>/ˈstɔːmi/</t>
+  </si>
+  <si>
+    <t>storm-y</t>
+  </si>
+  <si>
+    <t>/ˈreɪni/</t>
+  </si>
+  <si>
+    <t>rain-y</t>
+  </si>
+  <si>
+    <t>/ˈθʌndə(r)/</t>
+  </si>
+  <si>
+    <t>thun-der</t>
+  </si>
+  <si>
+    <t>/ˈlaɪtnɪŋ/</t>
+  </si>
+  <si>
+    <t>light-ning</t>
+  </si>
+  <si>
+    <t>/taɪˈfuːn/</t>
+  </si>
+  <si>
+    <t>ty-phoon</t>
+  </si>
+  <si>
+    <t>/flʌd/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -217,6 +322,14 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -226,12 +339,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -240,7 +368,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -251,6 +379,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -567,10 +698,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -580,10 +716,18 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3"/>
+      <c r="D1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>48</v>
+      </c>
       <c r="F1" s="3"/>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -593,8 +737,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="D2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -604,8 +754,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -615,8 +771,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -626,8 +788,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -637,8 +805,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -648,8 +822,14 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="D7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -659,8 +839,14 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -670,8 +856,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -681,8 +873,14 @@
       <c r="C10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -692,8 +890,14 @@
       <c r="C11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="D11" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -703,8 +907,14 @@
       <c r="C12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="D12" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -714,8 +924,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="D13" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -725,8 +941,14 @@
       <c r="C14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="D14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -736,8 +958,14 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -747,8 +975,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -758,8 +992,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -769,8 +1009,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -780,8 +1026,14 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -791,8 +1043,14 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -802,20 +1060,26 @@
       <c r="C21">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:5">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:5">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:5">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>

--- a/data/P1/P1T2_BQ4.xlsx
+++ b/data/P1/P1T2_BQ4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2E4E11-8F95-4546-85BC-A9615BF2EC45}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAB4834-A3A5-5643-AC3D-B54EF3922973}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29700" yWindow="4160" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="37580" yWindow="1420" windowWidth="30420" windowHeight="19880" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="103">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -279,6 +279,70 @@
   </si>
   <si>
     <t>/flʌd/</t>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>The first season with warm weather and new flowers</t>
+  </si>
+  <si>
+    <t>The hottest season with bright sunshine</t>
+  </si>
+  <si>
+    <t>The cool season when leaves turn yellow and fall down</t>
+  </si>
+  <si>
+    <t>The coldest season, sometimes with snow</t>
+  </si>
+  <si>
+    <t>Not hot, not cold, nice soft heat</t>
+  </si>
+  <si>
+    <t>Very high temperature, makes you feel sweaty</t>
+  </si>
+  <si>
+    <t>A little cold, comfortable after hot days</t>
+  </si>
+  <si>
+    <t>Low temperature, you need coats to stay warm</t>
+  </si>
+  <si>
+    <t>Water drops fall down from clouds</t>
+  </si>
+  <si>
+    <t>How hot, cold or wet the sky is each day</t>
+  </si>
+  <si>
+    <t>The sky drops white snow, ground is white</t>
+  </si>
+  <si>
+    <t>Many grey clouds cover the sky</t>
+  </si>
+  <si>
+    <t>The sun shines bright with few clouds</t>
+  </si>
+  <si>
+    <t>Strong air blows and moves trees</t>
+  </si>
+  <si>
+    <t>Bad weather with heavy rain and strong wind</t>
+  </si>
+  <si>
+    <t>Lots of rain falls all day</t>
+  </si>
+  <si>
+    <t>Loud big noise we hear in storms</t>
+  </si>
+  <si>
+    <t>Bright flash of light in dark storm sky</t>
+  </si>
+  <si>
+    <t>Very strong big wind storm with heavy rain</t>
+  </si>
+  <si>
+    <t>Too much rain covers roads and houses with water</t>
   </si>
 </sst>
 </file>
@@ -722,7 +786,9 @@
       <c r="E1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
@@ -743,6 +809,9 @@
       <c r="E2" t="s">
         <v>50</v>
       </c>
+      <c r="F2" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
@@ -760,6 +829,9 @@
       <c r="E3" t="s">
         <v>52</v>
       </c>
+      <c r="F3" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
@@ -777,6 +849,9 @@
       <c r="E4" t="s">
         <v>50</v>
       </c>
+      <c r="F4" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
@@ -794,6 +869,9 @@
       <c r="E5" t="s">
         <v>55</v>
       </c>
+      <c r="F5" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
@@ -811,6 +889,9 @@
       <c r="E6" t="s">
         <v>50</v>
       </c>
+      <c r="F6" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
@@ -828,6 +909,9 @@
       <c r="E7" t="s">
         <v>50</v>
       </c>
+      <c r="F7" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
@@ -845,6 +929,9 @@
       <c r="E8" t="s">
         <v>50</v>
       </c>
+      <c r="F8" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
@@ -862,6 +949,9 @@
       <c r="E9" t="s">
         <v>50</v>
       </c>
+      <c r="F9" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
@@ -879,6 +969,9 @@
       <c r="E10" t="s">
         <v>50</v>
       </c>
+      <c r="F10" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
@@ -896,6 +989,9 @@
       <c r="E11" t="s">
         <v>62</v>
       </c>
+      <c r="F11" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
@@ -913,6 +1009,9 @@
       <c r="E12" t="s">
         <v>64</v>
       </c>
+      <c r="F12" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
@@ -930,6 +1029,9 @@
       <c r="E13" t="s">
         <v>66</v>
       </c>
+      <c r="F13" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
@@ -947,6 +1049,9 @@
       <c r="E14" t="s">
         <v>68</v>
       </c>
+      <c r="F14" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
@@ -964,6 +1069,9 @@
       <c r="E15" t="s">
         <v>70</v>
       </c>
+      <c r="F15" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
@@ -981,8 +1089,11 @@
       <c r="E16" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -998,8 +1109,11 @@
       <c r="E17" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1015,8 +1129,11 @@
       <c r="E18" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>37</v>
       </c>
@@ -1032,8 +1149,11 @@
       <c r="E19" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -1049,8 +1169,11 @@
       <c r="E20" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -1066,20 +1189,23 @@
       <c r="E21" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="2"/>
       <c r="B26" s="1"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27" s="2"/>
       <c r="B27" s="1"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28" s="2"/>
       <c r="B28" s="1"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29" s="2"/>
       <c r="B29" s="1"/>
     </row>
